--- a/partner_results/ita/ClassMissingGermanDefinition_ita.xlsx
+++ b/partner_results/ita/ClassMissingGermanDefinition_ita.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tempering screw [ita]</t>
+          <t>tempering tool [ita]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Control variable for setting the temperature of the screw.</t>
+          <t>Control variable for setting the temperature of the tool.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -469,12 +469,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rolling [ita]</t>
+          <t>screw speed [ita]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Rolling is the second of the three areas of the extrusion line. Where the material is homogenised.</t>
+          <t>Control variable that indicates how high the speed of the screw is during extrusion.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -492,12 +492,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>agent [ita]</t>
+          <t>microcontroller [ita]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>An agent is a system that perceives its environment through sensors and can interact with it through actions.</t>
+          <t>Microcontrollers are compact integrated circuits designed to govern a specific operation in an embedded system. Typically a microcontroller includes a processor, memory and input/output peripherals on a single chip.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -515,12 +515,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>outlet surface [ita]</t>
+          <t>screw torque [ita]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>surface [dik]</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The outlet sourface of the extruder gives the extrudate its characteristic geometry.</t>
+          <t>Screw torque is a measured variable that indicates how high the torque of the screw is during extrusion.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -538,12 +538,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>screw torque [ita]</t>
+          <t>cylinder pressure [ita]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Screw torque is a measured variable that indicates how high the torque of the screw is during extrusion.</t>
+          <t>Measured variable that indicates how high the pressure in the cylinder is during extrusion.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -561,12 +561,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tempering feed roller [ita]</t>
+          <t>elastomer [ita]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>drop door temperature [dik]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Control variable for setting the temperature of the feed roller.</t>
+          <t>Elastomers are dimensionally stable but elastically deformable plastics. They are producest by vulcanization of rubber.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -584,12 +584,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>elastomer [ita]</t>
+          <t>rubber [ita]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>drop door temperature [dik]</t>
+          <t>polymer [chebi]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Elastomers are dimensionally stable but elastically deformable plastics. They are producest by vulcanization of rubber.</t>
+          <t>Rubber is an elastic substance made either from the juice of particular tropical trees or artificially. It is raw material for car tires and other technical products.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -607,12 +607,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>screw speed [ita]</t>
+          <t>agent [ita]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Control variable that indicates how high the speed of the screw is during extrusion.</t>
+          <t>An agent is a system that perceives its environment through sensors and can interact with it through actions.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -630,12 +630,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rubber [ita]</t>
+          <t>mixing temperature [ita]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>polymer [chebi]</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rubber is an elastic substance made either from the juice of particular tropical trees or artificially. It is raw material for car tires and other technical products.</t>
+          <t>Control variable that specifies at which temperature mixing takes place.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -653,12 +653,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>twin screw extruder [ita]</t>
+          <t>stamp pressure [ita]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>extruder</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Twin screw extruders have two screws, which have more shear and mixing capability than the single screw in a singel screw extruder. Depending on the direction of rotation of the screws, a distinction is made between counter-rotating and co-rotating twin-screw extruders.</t>
+          <t>Rücksprache DIK</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -676,12 +676,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>industry 4.0 [ita]</t>
+          <t>Extrusion throughput [ita]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>extensive quality</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Industry 4.0 is the intelligent networking of machines and processes in the industrial environment, with the help of information and communication technology and thus digitization of the industrial production.</t>
+          <t>The extrusion throughput indicates how many kilograms of material are extruded in a given unit of time.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -699,12 +699,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>online characterisation [ita]</t>
+          <t>tempering screw [ita]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Online characterisation is the characterization of the material properties during the process and on the real process line in order to be able to react to fluctuations during production.</t>
+          <t>Control variable for setting the temperature of the screw.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -722,12 +722,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stamp pressure [ita]</t>
+          <t>twin screw extruder [ita]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>extruder</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rücksprache DIK</t>
+          <t>Twin screw extruders have two screws, which have more shear and mixing capability than the single screw in a singel screw extruder. Depending on the direction of rotation of the screws, a distinction is made between counter-rotating and co-rotating twin-screw extruders.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -745,12 +745,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Extrusion throughput [ita]</t>
+          <t>extrusion pressure [ita]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>extensive quality</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The extrusion throughput indicates how many kilograms of material are extruded in a given unit of time.</t>
+          <t>Measured variable that indicates how high is the pressure during extrusion.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -768,12 +768,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mixing temperature [ita]</t>
+          <t>industry 4.0 [ita]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Control variable that specifies at which temperature mixing takes place.</t>
+          <t>Industry 4.0 is the intelligent networking of machines and processes in the industrial environment, with the help of information and communication technology and thus digitization of the industrial production.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -791,12 +791,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>extrusion pressure [ita]</t>
+          <t>tempering cylinder [ita]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Measured variable that indicates how high is the pressure during extrusion.</t>
+          <t>Control variable for setting the temperature of the cylinder.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>microcontroller [ita]</t>
+          <t>tempering feed roller [ita]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Microcontrollers are compact integrated circuits designed to govern a specific operation in an embedded system. Typically a microcontroller includes a processor, memory and input/output peripherals on a single chip.</t>
+          <t>Control variable for setting the temperature of the feed roller.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>online optimization [ita]</t>
+          <t>rolling [ita]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Online optimization is the adjustment of process parameters in the running process for process optimization.</t>
+          <t>Rolling is the second of the three areas of the extrusion line. Where the material is homogenised.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -860,12 +860,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tempering cylinder [ita]</t>
+          <t>online characterisation [ita]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Control variable for setting the temperature of the cylinder.</t>
+          <t>Online characterisation is the characterization of the material properties during the process and on the real process line in order to be able to react to fluctuations during production.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -883,12 +883,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cylinder pressure [ita]</t>
+          <t>outlet surface [ita]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>surface [dik]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Measured variable that indicates how high the pressure in the cylinder is during extrusion.</t>
+          <t>The outlet sourface of the extruder gives the extrudate its characteristic geometry.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -906,12 +906,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tempering tool [ita]</t>
+          <t>online optimization [ita]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Control variable for setting the temperature of the tool.</t>
+          <t>Online optimization is the adjustment of process parameters in the running process for process optimization.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
